--- a/storage/filtered_partial.xlsx
+++ b/storage/filtered_partial.xlsx
@@ -31,7 +31,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -48,18 +48,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="002E75B6"/>
         <bgColor rgb="002E75B6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DEEAF1"/>
-        <bgColor rgb="00DEEAF1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -81,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -94,18 +82,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -473,7 +449,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -507,155 +483,281 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Спальники  (8 поз.)</t>
+          <t xml:space="preserve">  Рюкзаки  (15 поз.)</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="n"/>
     </row>
-    <row r="3" outlineLevel="1" ht="32" customHeight="1">
+    <row r="3" outlineLevel="1" ht="18" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Спальный мешок Alexika Canada Plus, оливковый правый</t>
+          <t>Рюкзак Bach Pack Daydream 65 Long, black</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Спальный мешок Alexika Canada Plus</t>
+          <t>Рюкзак Bach Pack Daydream 65 Long</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>24499</v>
+        <v>46899</v>
       </c>
     </row>
     <row r="4" outlineLevel="1" ht="32" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Спальный мешок Alexika Siberia Plus, зеленый левый</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Спальный мешок Alexika Siberia Plus</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>16399</v>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Рюкзак Bach Pack Daydream 65 Long, Picante red</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Рюкзак Bach Pack Daydream 65 Long</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>46899</v>
       </c>
     </row>
     <row r="5" outlineLevel="1" ht="32" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Спальный мешок Alexika Siberia Plus, зеленый правый</t>
+          <t>Рюкзак Deuter Aircontact Core 65+10 SL, chestnut/umbra</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Спальный мешок Alexika Siberia Plus</t>
+          <t>Рюкзак Deuter Aircontact Core 65+10 SL</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>16399</v>
+        <v>38799</v>
       </c>
     </row>
     <row r="6" outlineLevel="1" ht="32" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Спальный мешок Alexika Siberia Wide Plus, оливковый правый</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Спальный мешок Alexika Siberia Wide Plus</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>17999</v>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Рюкзак Deuter Trans Alpine 24, atlantic/lnk</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Рюкзак Deuter Trans Alpine 24</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>18499</v>
       </c>
     </row>
     <row r="7" outlineLevel="1" ht="32" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Спальный мешок Alexika Tundra Plus, синий правый</t>
+          <t>Рюкзак Deuter Trans Alpine 24, sprout/cactus, M</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Спальный мешок Alexika Tundra Plus</t>
+          <t>Рюкзак Deuter Trans Alpine 24</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>18799</v>
-      </c>
-    </row>
-    <row r="8" outlineLevel="1" ht="32" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Спальный мешок Tramp Kingwood Wide,  правый</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Спальный мешок Tramp Kingwood Wide</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>9199</v>
-      </c>
-    </row>
-    <row r="9" outlineLevel="1" ht="32" customHeight="1">
+        <v>18499</v>
+      </c>
+    </row>
+    <row r="8" outlineLevel="1" ht="18" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Рюкзак Kanrock Cruiser 45, anthracite</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Рюкзак Kanrock Cruiser 45</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>15999</v>
+      </c>
+    </row>
+    <row r="9" outlineLevel="1" ht="18" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Спальный мешок Tramp Sherwood Wide,  левый</t>
+          <t>Рюкзак Kanrock Moveit 21, sea green</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Спальный мешок Tramp Sherwood Wide</t>
+          <t>Рюкзак Kanrock Moveit 21</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>7999</v>
-      </c>
-    </row>
-    <row r="10" outlineLevel="1" ht="32" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Спальный мешок Totem Hunter, олива правый</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Спальный мешок Totem Hunter</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>2599</v>
+        <v>7499</v>
+      </c>
+    </row>
+    <row r="10" outlineLevel="1" ht="18" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Рюкзак Osprey Atmos AG 65, зеленый, S/M</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Рюкзак Osprey Atmos AG 65</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>52149</v>
+      </c>
+    </row>
+    <row r="11" outlineLevel="1" ht="32" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Рюкзак Osprey Eja 38 W, Purple Dusk, XS/S</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Рюкзак Osprey Eja 38 W</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>34749</v>
+      </c>
+    </row>
+    <row r="12" outlineLevel="1" ht="32" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Рюкзак Osprey Eja Pro 55 W, Dale Grey/Poinsettia Red, M/L</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Рюкзак Osprey Eja Pro 55 W</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>41149</v>
+      </c>
+    </row>
+    <row r="13" outlineLevel="1" ht="32" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Рюкзак Osprey Eja Pro 55 W, Dale Grey/Poinsettia Red, XS/S</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Рюкзак Osprey Eja Pro 55 W</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>41149</v>
+      </c>
+    </row>
+    <row r="14" outlineLevel="1" ht="32" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Рюкзак Osprey Exos Pro 55 , Dale Grey/Agam Blue, L/XL</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Рюкзак Osprey Exos Pro 55</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>41149</v>
+      </c>
+    </row>
+    <row r="15" outlineLevel="1" ht="32" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Рюкзак Osprey Exos Pro 55 , Dale Grey/Agam Blue, S/M</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Рюкзак Osprey Exos Pro 55</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>41149</v>
+      </c>
+    </row>
+    <row r="16" outlineLevel="1" ht="18" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Накидка на рюкзак Tramp 20-35л.,</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Tramp</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="17" outlineLevel="1" ht="32" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Накидка на рюкзак Goraa XL, 65-85л., зеленый,</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>2499</v>
       </c>
     </row>
   </sheetData>
